--- a/public/templates/05_입출금_자금일보_월보/자금관리_입출금_일보_월보_자금계획.xlsx
+++ b/public/templates/05_입출금_자금일보_월보/자금관리_입출금_일보_월보_자금계획.xlsx
@@ -2388,185 +2388,369 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="15"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="16" t="str">
+      <c r="A3" s="15" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>입금</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>매출대금</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>○○전자</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>8월 납품대금</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="n">
+        <v>12500000</v>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>주거래통장</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>계좌이체</t>
+        </is>
+      </c>
+      <c r="I3" s="16" t="n">
         <f aca="false">IF(OR($A3="",$F3=""),"",IF($B3="입금",$F3,0))</f>
-        <v/>
-      </c>
-      <c r="J3" s="16" t="str">
+        <v>12500000</v>
+      </c>
+      <c r="J3" s="16" t="n">
         <f aca="false">IF(OR($A3="",$F3=""),"",IF($B3="출금",$F3,0))</f>
-        <v/>
-      </c>
-      <c r="K3" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="K3" s="17" t="n">
         <f aca="false">IF($A3="","",COUNTIFS($A$3:$A3,$A3))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="L3" s="17" t="str">
         <f aca="false">IF($A3="","",TEXT($A3,"yyyymmdd")&amp;"|"&amp;$K3)</f>
-        <v/>
+        <v>20260901|1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="15"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="16" t="str">
+      <c r="A4" s="15" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>출금</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>매입대금</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>△△소재</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>원자재 대금</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="n">
+        <v>4800000</v>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>주거래통장</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>계좌이체</t>
+        </is>
+      </c>
+      <c r="I4" s="16" t="n">
         <f aca="false">IF(OR($A4="",$F4=""),"",IF($B4="입금",$F4,0))</f>
-        <v/>
-      </c>
-      <c r="J4" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="J4" s="16" t="n">
         <f aca="false">IF(OR($A4="",$F4=""),"",IF($B4="출금",$F4,0))</f>
-        <v/>
-      </c>
-      <c r="K4" s="17" t="str">
+        <v>4800000</v>
+      </c>
+      <c r="K4" s="17" t="n">
         <f aca="false">IF($A4="","",COUNTIFS($A$3:$A4,$A4))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="L4" s="17" t="str">
         <f aca="false">IF($A4="","",TEXT($A4,"yyyymmdd")&amp;"|"&amp;$K4)</f>
-        <v/>
+        <v>20260902|1</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="15"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
+      <c r="A5" s="15" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>출금</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>공과금</t>
+        </is>
+      </c>
       <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="16" t="str">
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>8월 전기요금</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>640000</v>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>주거래통장</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>카드</t>
+        </is>
+      </c>
+      <c r="I5" s="16" t="n">
         <f aca="false">IF(OR($A5="",$F5=""),"",IF($B5="입금",$F5,0))</f>
-        <v/>
-      </c>
-      <c r="J5" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="J5" s="16" t="n">
         <f aca="false">IF(OR($A5="",$F5=""),"",IF($B5="출금",$F5,0))</f>
-        <v/>
-      </c>
-      <c r="K5" s="17" t="str">
+        <v>640000</v>
+      </c>
+      <c r="K5" s="17" t="n">
         <f aca="false">IF($A5="","",COUNTIFS($A$3:$A5,$A5))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="L5" s="17" t="str">
         <f aca="false">IF($A5="","",TEXT($A5,"yyyymmdd")&amp;"|"&amp;$K5)</f>
-        <v/>
+        <v>20260902|2</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="15"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="16" t="str">
+      <c r="A6" s="15" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>입금</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>매출대금</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>○○전자</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>샘플 대금</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>주거래통장</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>계좌이체</t>
+        </is>
+      </c>
+      <c r="I6" s="16" t="n">
         <f aca="false">IF(OR($A6="",$F6=""),"",IF($B6="입금",$F6,0))</f>
-        <v/>
-      </c>
-      <c r="J6" s="16" t="str">
+        <v>3200000</v>
+      </c>
+      <c r="J6" s="16" t="n">
         <f aca="false">IF(OR($A6="",$F6=""),"",IF($B6="출금",$F6,0))</f>
-        <v/>
-      </c>
-      <c r="K6" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="K6" s="17" t="n">
         <f aca="false">IF($A6="","",COUNTIFS($A$3:$A6,$A6))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="L6" s="17" t="str">
         <f aca="false">IF($A6="","",TEXT($A6,"yyyymmdd")&amp;"|"&amp;$K6)</f>
-        <v/>
+        <v>20260902|3</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="15"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
+      <c r="A7" s="15" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>출금</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>급여</t>
+        </is>
+      </c>
       <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="16" t="str">
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>8월 급여</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>9200000</v>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>급여통장</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>계좌이체</t>
+        </is>
+      </c>
+      <c r="I7" s="16" t="n">
         <f aca="false">IF(OR($A7="",$F7=""),"",IF($B7="입금",$F7,0))</f>
-        <v/>
-      </c>
-      <c r="J7" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="J7" s="16" t="n">
         <f aca="false">IF(OR($A7="",$F7=""),"",IF($B7="출금",$F7,0))</f>
-        <v/>
-      </c>
-      <c r="K7" s="17" t="str">
+        <v>9200000</v>
+      </c>
+      <c r="K7" s="17" t="n">
         <f aca="false">IF($A7="","",COUNTIFS($A$3:$A7,$A7))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="L7" s="17" t="str">
         <f aca="false">IF($A7="","",TEXT($A7,"yyyymmdd")&amp;"|"&amp;$K7)</f>
-        <v/>
+        <v>20260905|1</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="15"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
+      <c r="A8" s="15" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>출금</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>임차료</t>
+        </is>
+      </c>
       <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="16" t="str">
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>9월 공장 임차료</t>
+        </is>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>주거래통장</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>계좌이체</t>
+        </is>
+      </c>
+      <c r="I8" s="16" t="n">
         <f aca="false">IF(OR($A8="",$F8=""),"",IF($B8="입금",$F8,0))</f>
-        <v/>
-      </c>
-      <c r="J8" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="J8" s="16" t="n">
         <f aca="false">IF(OR($A8="",$F8=""),"",IF($B8="출금",$F8,0))</f>
-        <v/>
-      </c>
-      <c r="K8" s="17" t="str">
+        <v>1800000</v>
+      </c>
+      <c r="K8" s="17" t="n">
         <f aca="false">IF($A8="","",COUNTIFS($A$3:$A8,$A8))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="L8" s="17" t="str">
         <f aca="false">IF($A8="","",TEXT($A8,"yyyymmdd")&amp;"|"&amp;$K8)</f>
-        <v/>
+        <v>20260908|1</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="15"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="16" t="str">
+      <c r="A9" s="15" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>입금</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>매출대금</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>○○전자</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>9월 중간 정산</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>5400000</v>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>주거래통장</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>계좌이체</t>
+        </is>
+      </c>
+      <c r="I9" s="16" t="n">
         <f aca="false">IF(OR($A9="",$F9=""),"",IF($B9="입금",$F9,0))</f>
-        <v/>
-      </c>
-      <c r="J9" s="16" t="str">
+        <v>5400000</v>
+      </c>
+      <c r="J9" s="16" t="n">
         <f aca="false">IF(OR($A9="",$F9=""),"",IF($B9="출금",$F9,0))</f>
-        <v/>
-      </c>
-      <c r="K9" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="K9" s="17" t="n">
         <f aca="false">IF($A9="","",COUNTIFS($A$3:$A9,$A9))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="L9" s="17" t="str">
         <f aca="false">IF($A9="","",TEXT($A9,"yyyymmdd")&amp;"|"&amp;$K9)</f>
-        <v/>
+        <v>20260914|1</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23254,7 +23438,7 @@
         <v>59</v>
       </c>
       <c r="B3" s="18" t="n">
-        <v>46086</v>
+        <v>46267</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>60</v>
@@ -23267,7 +23451,7 @@
       <c r="B5" s="19"/>
       <c r="C5" s="20" t="n">
         <f aca="false">계좌목록!$D$24+SUMIFS(입출금내역!$I$3:$I$802,입출금내역!$A$3:$A$802,"&lt;"&amp;$B$3)-SUMIFS(입출금내역!$J$3:$J$802,입출금내역!$A$3:$A$802,"&lt;"&amp;$B$3)</f>
-        <v>55000000</v>
+        <v>67500000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23277,7 +23461,7 @@
       <c r="B6" s="19"/>
       <c r="C6" s="20" t="n">
         <f aca="false">SUMIFS(입출금내역!$I$3:$I$802,입출금내역!$A$3:$A$802,$B$3)</f>
-        <v>0</v>
+        <v>3200000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23287,7 +23471,7 @@
       <c r="B7" s="19"/>
       <c r="C7" s="20" t="n">
         <f aca="false">SUMIFS(입출금내역!$J$3:$J$802,입출금내역!$A$3:$A$802,$B$3)</f>
-        <v>0</v>
+        <v>5440000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23326,23 +23510,23 @@
       </c>
       <c r="B11" s="17" t="str">
         <f aca="false">IFERROR(INDEX(입출금내역!$B$3:$B$802,MATCH(TEXT($B$3,"yyyymmdd")&amp;"|"&amp;1,입출금내역!$L$3:$L$802,0)),"")</f>
-        <v/>
+        <v>출금</v>
       </c>
       <c r="C11" s="17" t="str">
         <f aca="false">IF($B11="","",IFERROR(IF(INDEX(입출금내역!$C$3:$C$802,MATCH(TEXT($B$3,"yyyymmdd")&amp;"|"&amp;1,입출금내역!$L$3:$L$802,0))="","",INDEX(입출금내역!$C$3:$C$802,MATCH(TEXT($B$3,"yyyymmdd")&amp;"|"&amp;1,입출금내역!$L$3:$L$802,0))),""))</f>
-        <v/>
+        <v>매입대금</v>
       </c>
       <c r="D11" s="17" t="str">
         <f aca="false">IF($B11="","",IFERROR(IF(INDEX(입출금내역!$D$3:$D$802,MATCH(TEXT($B$3,"yyyymmdd")&amp;"|"&amp;1,입출금내역!$L$3:$L$802,0))="","",INDEX(입출금내역!$D$3:$D$802,MATCH(TEXT($B$3,"yyyymmdd")&amp;"|"&amp;1,입출금내역!$L$3:$L$802,0))),""))</f>
-        <v/>
+        <v>△△소재</v>
       </c>
       <c r="E11" s="17" t="str">
         <f aca="false">IF($B11="","",IFERROR(IF(INDEX(입출금내역!$E$3:$E$802,MATCH(TEXT($B$3,"yyyymmdd")&amp;"|"&amp;1,입출금내역!$L$3:$L$802,0))="","",INDEX(입출금내역!$E$3:$E$802,MATCH(TEXT($B$3,"yyyymmdd")&amp;"|"&amp;1,입출금내역!$L$3:$L$802,0))),""))</f>
-        <v/>
-      </c>
-      <c r="F11" s="16" t="str">
+        <v>원자재 대금</v>
+      </c>
+      <c r="F11" s="16" t="n">
         <f aca="false">IF($B11="","",IFERROR(INDEX(입출금내역!$F$3:$F$802,MATCH(TEXT($B$3,"yyyymmdd")&amp;"|"&amp;1,입출금내역!$L$3:$L$802,0)),""))</f>
-        <v/>
+        <v>4800000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23351,11 +23535,11 @@
       </c>
       <c r="B12" s="17" t="str">
         <f aca="false">IFERROR(INDEX(입출금내역!$B$3:$B$802,MATCH(TEXT($B$3,"yyyymmdd")&amp;"|"&amp;2,입출금내역!$L$3:$L$802,0)),"")</f>
-        <v/>
+        <v>출금</v>
       </c>
       <c r="C12" s="17" t="str">
         <f aca="false">IF($B12="","",IFERROR(IF(INDEX(입출금내역!$C$3:$C$802,MATCH(TEXT($B$3,"yyyymmdd")&amp;"|"&amp;2,입출금내역!$L$3:$L$802,0))="","",INDEX(입출금내역!$C$3:$C$802,MATCH(TEXT($B$3,"yyyymmdd")&amp;"|"&amp;2,입출금내역!$L$3:$L$802,0))),""))</f>
-        <v/>
+        <v>공과금</v>
       </c>
       <c r="D12" s="17" t="str">
         <f aca="false">IF($B12="","",IFERROR(IF(INDEX(입출금내역!$D$3:$D$802,MATCH(TEXT($B$3,"yyyymmdd")&amp;"|"&amp;2,입출금내역!$L$3:$L$802,0))="","",INDEX(입출금내역!$D$3:$D$802,MATCH(TEXT($B$3,"yyyymmdd")&amp;"|"&amp;2,입출금내역!$L$3:$L$802,0))),""))</f>
@@ -23363,11 +23547,11 @@
       </c>
       <c r="E12" s="17" t="str">
         <f aca="false">IF($B12="","",IFERROR(IF(INDEX(입출금내역!$E$3:$E$802,MATCH(TEXT($B$3,"yyyymmdd")&amp;"|"&amp;2,입출금내역!$L$3:$L$802,0))="","",INDEX(입출금내역!$E$3:$E$802,MATCH(TEXT($B$3,"yyyymmdd")&amp;"|"&amp;2,입출금내역!$L$3:$L$802,0))),""))</f>
-        <v/>
-      </c>
-      <c r="F12" s="16" t="str">
+        <v>8월 전기요금</v>
+      </c>
+      <c r="F12" s="16" t="n">
         <f aca="false">IF($B12="","",IFERROR(INDEX(입출금내역!$F$3:$F$802,MATCH(TEXT($B$3,"yyyymmdd")&amp;"|"&amp;2,입출금내역!$L$3:$L$802,0)),""))</f>
-        <v/>
+        <v>640000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23376,23 +23560,23 @@
       </c>
       <c r="B13" s="17" t="str">
         <f aca="false">IFERROR(INDEX(입출금내역!$B$3:$B$802,MATCH(TEXT($B$3,"yyyymmdd")&amp;"|"&amp;3,입출금내역!$L$3:$L$802,0)),"")</f>
-        <v/>
+        <v>입금</v>
       </c>
       <c r="C13" s="17" t="str">
         <f aca="false">IF($B13="","",IFERROR(IF(INDEX(입출금내역!$C$3:$C$802,MATCH(TEXT($B$3,"yyyymmdd")&amp;"|"&amp;3,입출금내역!$L$3:$L$802,0))="","",INDEX(입출금내역!$C$3:$C$802,MATCH(TEXT($B$3,"yyyymmdd")&amp;"|"&amp;3,입출금내역!$L$3:$L$802,0))),""))</f>
-        <v/>
+        <v>매출대금</v>
       </c>
       <c r="D13" s="17" t="str">
         <f aca="false">IF($B13="","",IFERROR(IF(INDEX(입출금내역!$D$3:$D$802,MATCH(TEXT($B$3,"yyyymmdd")&amp;"|"&amp;3,입출금내역!$L$3:$L$802,0))="","",INDEX(입출금내역!$D$3:$D$802,MATCH(TEXT($B$3,"yyyymmdd")&amp;"|"&amp;3,입출금내역!$L$3:$L$802,0))),""))</f>
-        <v/>
+        <v>○○전자</v>
       </c>
       <c r="E13" s="17" t="str">
         <f aca="false">IF($B13="","",IFERROR(IF(INDEX(입출금내역!$E$3:$E$802,MATCH(TEXT($B$3,"yyyymmdd")&amp;"|"&amp;3,입출금내역!$L$3:$L$802,0))="","",INDEX(입출금내역!$E$3:$E$802,MATCH(TEXT($B$3,"yyyymmdd")&amp;"|"&amp;3,입출금내역!$L$3:$L$802,0))),""))</f>
-        <v/>
-      </c>
-      <c r="F13" s="16" t="str">
+        <v>샘플 대금</v>
+      </c>
+      <c r="F13" s="16" t="n">
         <f aca="false">IF($B13="","",IFERROR(INDEX(입출금내역!$F$3:$F$802,MATCH(TEXT($B$3,"yyyymmdd")&amp;"|"&amp;3,입출금내역!$L$3:$L$802,0)),""))</f>
-        <v/>
+        <v>3200000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -24229,23 +24413,23 @@
       </c>
       <c r="B14" s="26" t="n">
         <f aca="false">SUMIFS(입출금내역!$I$3:$I$802,입출금내역!$A$3:$A$802,"&gt;="&amp;DATE($B$3,9,1),입출금내역!$A$3:$A$802,"&lt;="&amp;EOMONTH(DATE($B$3,9,1),0))</f>
-        <v>0</v>
+        <v>21100000</v>
       </c>
       <c r="C14" s="26" t="n">
         <f aca="false">SUMIFS(입출금내역!$J$3:$J$802,입출금내역!$A$3:$A$802,"&gt;="&amp;DATE($B$3,9,1),입출금내역!$A$3:$A$802,"&lt;="&amp;EOMONTH(DATE($B$3,9,1),0))</f>
-        <v>0</v>
+        <v>16440000</v>
       </c>
       <c r="D14" s="26" t="n">
         <f aca="false">$B14-$C14</f>
-        <v>0</v>
+        <v>4660000</v>
       </c>
       <c r="E14" s="26" t="n">
         <f aca="false">계좌목록!$D$24+SUMIFS(입출금내역!$I$3:$I$802,입출금내역!$A$3:$A$802,"&lt;="&amp;EOMONTH(DATE($B$3,9,1),0))-SUMIFS(입출금내역!$J$3:$J$802,입출금내역!$A$3:$A$802,"&lt;="&amp;EOMONTH(DATE($B$3,9,1),0))</f>
-        <v>55000000</v>
+        <v>59660000</v>
       </c>
       <c r="F14" s="24" t="n">
         <f aca="false">COUNTIFS(입출금내역!$A$3:$A$802,"&gt;="&amp;DATE($B$3,9,1),입출금내역!$A$3:$A$802,"&lt;="&amp;EOMONTH(DATE($B$3,9,1),0))</f>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -24266,7 +24450,7 @@
       </c>
       <c r="E15" s="26" t="n">
         <f aca="false">계좌목록!$D$24+SUMIFS(입출금내역!$I$3:$I$802,입출금내역!$A$3:$A$802,"&lt;="&amp;EOMONTH(DATE($B$3,10,1),0))-SUMIFS(입출금내역!$J$3:$J$802,입출금내역!$A$3:$A$802,"&lt;="&amp;EOMONTH(DATE($B$3,10,1),0))</f>
-        <v>55000000</v>
+        <v>59660000</v>
       </c>
       <c r="F15" s="24" t="n">
         <f aca="false">COUNTIFS(입출금내역!$A$3:$A$802,"&gt;="&amp;DATE($B$3,10,1),입출금내역!$A$3:$A$802,"&lt;="&amp;EOMONTH(DATE($B$3,10,1),0))</f>
@@ -24291,7 +24475,7 @@
       </c>
       <c r="E16" s="26" t="n">
         <f aca="false">계좌목록!$D$24+SUMIFS(입출금내역!$I$3:$I$802,입출금내역!$A$3:$A$802,"&lt;="&amp;EOMONTH(DATE($B$3,11,1),0))-SUMIFS(입출금내역!$J$3:$J$802,입출금내역!$A$3:$A$802,"&lt;="&amp;EOMONTH(DATE($B$3,11,1),0))</f>
-        <v>55000000</v>
+        <v>59660000</v>
       </c>
       <c r="F16" s="24" t="n">
         <f aca="false">COUNTIFS(입출금내역!$A$3:$A$802,"&gt;="&amp;DATE($B$3,11,1),입출금내역!$A$3:$A$802,"&lt;="&amp;EOMONTH(DATE($B$3,11,1),0))</f>
@@ -24316,7 +24500,7 @@
       </c>
       <c r="E17" s="26" t="n">
         <f aca="false">계좌목록!$D$24+SUMIFS(입출금내역!$I$3:$I$802,입출금내역!$A$3:$A$802,"&lt;="&amp;EOMONTH(DATE($B$3,12,1),0))-SUMIFS(입출금내역!$J$3:$J$802,입출금내역!$A$3:$A$802,"&lt;="&amp;EOMONTH(DATE($B$3,12,1),0))</f>
-        <v>55000000</v>
+        <v>59660000</v>
       </c>
       <c r="F17" s="24" t="n">
         <f aca="false">COUNTIFS(입출금내역!$A$3:$A$802,"&gt;="&amp;DATE($B$3,12,1),입출금내역!$A$3:$A$802,"&lt;="&amp;EOMONTH(DATE($B$3,12,1),0))</f>
@@ -24329,20 +24513,20 @@
       </c>
       <c r="B18" s="28" t="n">
         <f aca="false">SUM(B6:B17)</f>
-        <v>0</v>
+        <v>21100000</v>
       </c>
       <c r="C18" s="28" t="n">
         <f aca="false">SUM(C6:C17)</f>
-        <v>0</v>
+        <v>16440000</v>
       </c>
       <c r="D18" s="28" t="n">
         <f aca="false">SUM(D6:D17)</f>
-        <v>0</v>
+        <v>4660000</v>
       </c>
       <c r="E18" s="27"/>
       <c r="F18" s="27" t="n">
         <f aca="false">SUM(F6:F17)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -24420,68 +24604,176 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="15"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
+      <c r="A3" s="15" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>출금</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>급여</t>
+        </is>
+      </c>
       <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="10"/>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>8월 급여</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="n">
+        <v>9200000</v>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>실행완료</t>
+        </is>
+      </c>
       <c r="H3" s="30" t="str">
         <f aca="true">IF(OR($A3="",$G3="실행완료"),"",$A3-TODAY())</f>
         <v/>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="15"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="30" t="str">
+      <c r="A4" s="15" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>입금</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>매출대금</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>○○전자</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>9월 잔금 예정</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="H4" s="30" t="n">
         <f aca="true">IF(OR($A4="",$G4="실행완료"),"",$A4-TODAY())</f>
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="15"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="30" t="str">
+      <c r="A5" s="15" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>출금</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>매입대금</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>△△소재</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>9월 원자재 대금</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>5200000</v>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="H5" s="30" t="n">
         <f aca="true">IF(OR($A5="",$G5="실행완료"),"",$A5-TODAY())</f>
-        <v/>
+        <v>11</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="15"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
+      <c r="A6" s="15" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>출금</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>세금</t>
+        </is>
+      </c>
       <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="30" t="str">
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>부가세 예정고지</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="H6" s="30" t="n">
         <f aca="true">IF(OR($A6="",$G6="실행완료"),"",$A6-TODAY())</f>
-        <v/>
+        <v>11</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="15"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
+      <c r="A7" s="15" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>출금</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>급여</t>
+        </is>
+      </c>
       <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="30" t="str">
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>9월 급여</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>9300000</v>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="H7" s="30" t="n">
         <f aca="true">IF(OR($A7="",$G7="실행완료"),"",$A7-TODAY())</f>
-        <v/>
+        <v>21</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27033,7 +27325,7 @@
       <c r="D205" s="19"/>
       <c r="E205" s="20" t="n">
         <f aca="true">SUMIFS(자금계획!$F$3:$F$202,자금계획!$B$3:$B$202,"입금",자금계획!$G$3:$G$202,"예정",자금계획!$A$3:$A$202,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+0,1),자금계획!$A$3:$A$202,"&lt;="&amp;EOMONTH(DATE(YEAR(TODAY()),MONTH(TODAY())+0,1),0))</f>
-        <v>0</v>
+        <v>8000000</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27045,7 +27337,7 @@
       <c r="D206" s="19"/>
       <c r="E206" s="20" t="n">
         <f aca="true">SUMIFS(자금계획!$F$3:$F$202,자금계획!$B$3:$B$202,"출금",자금계획!$G$3:$G$202,"예정",자금계획!$A$3:$A$202,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+0,1),자금계획!$A$3:$A$202,"&lt;="&amp;EOMONTH(DATE(YEAR(TODAY()),MONTH(TODAY())+0,1),0))</f>
-        <v>0</v>
+        <v>7600000</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27069,7 +27361,7 @@
       <c r="D208" s="19"/>
       <c r="E208" s="20" t="n">
         <f aca="true">SUMIFS(자금계획!$F$3:$F$202,자금계획!$B$3:$B$202,"출금",자금계획!$G$3:$G$202,"예정",자금계획!$A$3:$A$202,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),자금계획!$A$3:$A$202,"&lt;="&amp;EOMONTH(DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),0))</f>
-        <v>0</v>
+        <v>9300000</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27081,7 +27373,7 @@
       <c r="D209" s="21"/>
       <c r="E209" s="22" t="n">
         <f aca="true">계좌목록!$D$24+SUMIFS(입출금내역!$I$3:$I$802,입출금내역!$A$3:$A$802,"&lt;="&amp;TODAY())-SUMIFS(입출금내역!$J$3:$J$802,입출금내역!$A$3:$A$802,"&lt;="&amp;TODAY())+B205-B206</f>
-        <v>55000000</v>
+        <v>59660000</v>
       </c>
     </row>
   </sheetData>
@@ -27176,39 +27468,105 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="10"/>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="30" t="str">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>받을어음</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C3" s="15" t="n">
+        <v>46336</v>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>○○전자</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>가나12345678</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>미결제</t>
+        </is>
+      </c>
+      <c r="H3" s="30" t="n">
         <f aca="true">IF(OR($C3="",$G3="결제완료"),"",$C3-TODAY())</f>
-        <v/>
+        <v>57</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10"/>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="30" t="str">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>지급어음</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="n">
+        <v>46223</v>
+      </c>
+      <c r="C4" s="15" t="n">
+        <v>46285</v>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>△△소재</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>다라87654321</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>미결제</t>
+        </is>
+      </c>
+      <c r="H4" s="30" t="n">
         <f aca="true">IF(OR($C4="",$G4="결제완료"),"",$C4-TODAY())</f>
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10"/>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="10"/>
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>받을어음</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="n">
+        <v>46157</v>
+      </c>
+      <c r="C5" s="15" t="n">
+        <v>46249</v>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>○○전자</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>가나12345677</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>4200000</v>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>결제완료</t>
+        </is>
+      </c>
       <c r="H5" s="30" t="str">
         <f aca="true">IF(OR($C5="",$G5="결제완료"),"",$C5-TODAY())</f>
         <v/>
@@ -28482,7 +28840,7 @@
       <c r="E104" s="32"/>
       <c r="F104" s="12" t="n">
         <f aca="false">SUMIFS($F$3:$F$102,$A$3:$A$102,"받을어음",$G$3:$G$102,"미결제")</f>
-        <v>0</v>
+        <v>6000000</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28492,7 +28850,7 @@
       <c r="E105" s="32"/>
       <c r="F105" s="12" t="n">
         <f aca="false">SUMIFS($F$3:$F$102,$A$3:$A$102,"지급어음",$G$3:$G$102,"미결제")</f>
-        <v>0</v>
+        <v>3500000</v>
       </c>
     </row>
   </sheetData>
@@ -28585,29 +28943,65 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="33"/>
-      <c r="H3" s="30" t="str">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>○○은행</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>운전자금대출</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="n">
+        <v>45718</v>
+      </c>
+      <c r="D3" s="15" t="n">
+        <v>46297</v>
+      </c>
+      <c r="E3" s="11" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="F3" s="11" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="G3" s="33" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="H3" s="30" t="n">
         <f aca="true">IF($D3="","",$D3-TODAY())</f>
-        <v/>
+        <v>18</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="33"/>
-      <c r="H4" s="30" t="str">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>△△은행</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>시설자금대출</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="n">
+        <v>45458</v>
+      </c>
+      <c r="D4" s="15" t="n">
+        <v>47284</v>
+      </c>
+      <c r="E4" s="11" t="n">
+        <v>200000000</v>
+      </c>
+      <c r="F4" s="11" t="n">
+        <v>145000000</v>
+      </c>
+      <c r="G4" s="33" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="H4" s="30" t="n">
         <f aca="true">IF($D4="","",$D4-TODAY())</f>
-        <v/>
+        <v>1005</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29110,7 +29504,7 @@
       </c>
       <c r="F44" s="12" t="n">
         <f aca="false">SUM(F3:F42)</f>
-        <v>0</v>
+        <v>185000000</v>
       </c>
     </row>
   </sheetData>
